--- a/交易/外匯交易記錄.xlsx
+++ b/交易/外匯交易記錄.xlsx
@@ -19,16 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>交易品種</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交易日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>持倉狀態</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -59,6 +55,23 @@
   <si>
     <t>交易感悟</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已平倉</t>
+  </si>
+  <si>
+    <t>GBPJPY</t>
+  </si>
+  <si>
+    <t>開倉日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平倉日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -66,7 +79,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -141,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -149,16 +162,584 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0066FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0066FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0066FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0066FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <color rgb="FFFC04EA"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0066FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <color rgb="FFFC04EA"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0066FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0066FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <color rgb="FFFC04EA"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0066FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <color rgb="FFFC04EA"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <color rgb="FFFC04EA"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <color rgb="FFFC04EA"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFC04EA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0066FF"/>
+      <color rgb="FF3333FF"/>
+      <color rgb="FFFC04EA"/>
+      <color rgb="FFF4C20C"/>
+      <color rgb="FFF93B07"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -433,63 +1014,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="21.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
-    <col min="5" max="5" width="16.875" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="15.75" customWidth="1"/>
-    <col min="8" max="8" width="19.125" customWidth="1"/>
-    <col min="9" max="9" width="11.5" customWidth="1"/>
-    <col min="10" max="10" width="42.875" customWidth="1"/>
+    <col min="2" max="3" width="21.375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="18.125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="16.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="26" style="5" customWidth="1"/>
+    <col min="8" max="8" width="37.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="5" customWidth="1"/>
+    <col min="11" max="11" width="42.875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="21">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>9</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+      <formula>"已平倉"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+      <formula>"持倉中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="notContainsText" dxfId="13" priority="5" operator="notContains" text="USD">
+      <formula>ISERROR(SEARCH("USD",A2))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="USD">
+      <formula>NOT(ISERROR(SEARCH("USD",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"N"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+      <formula>"Y"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+      <formula>"N"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
       <formula1>"USDCHF,USDJPY,USDCAD,EURUSD,EURJPY,EURGBP,GBPUSD,GBPJPY,CHFJPY,XAUUSD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"持倉中,已平倉"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576 I2:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576 J2:J1048576">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
